--- a/results/naturverbundenheit/explaining_features/nature-dataset-optimal_explainable_features-jensenshannon-auto.xlsx
+++ b/results/naturverbundenheit/explaining_features/nature-dataset-optimal_explainable_features-jensenshannon-auto.xlsx
@@ -517,7 +517,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3368984069032256</v>
+        <v>0.3803763845691754</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
